--- a/artfynd/A 3607-2023 artfynd.xlsx
+++ b/artfynd/A 3607-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3607-2023 artfynd.xlsx
+++ b/artfynd/A 3607-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81217222</v>
+        <v>81217235</v>
       </c>
       <c r="B2" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>415777.9236777688</v>
+        <v>415787</v>
       </c>
       <c r="R2" t="n">
-        <v>6432341.204376015</v>
+        <v>6432398</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2019-08-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,53 +781,68 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81217229</v>
+        <v>86449766</v>
       </c>
       <c r="B3" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220079</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Falköpings kommun, Vg</t>
+          <t>Betesmark norr om Åsarp, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415779.0468420109</v>
+        <v>415682</v>
       </c>
       <c r="R3" t="n">
-        <v>6432369.259199382</v>
+        <v>6432351</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,27 +866,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,75 +880,87 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Carin Franson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
-        </is>
-      </c>
+          <t>Carin Franson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81217224</v>
+        <v>86449907</v>
       </c>
       <c r="B4" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221849</v>
+        <v>219875</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Falköpings kommun, Vg</t>
+          <t>Betesmark norr om Åsarp, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>415655.897124836</v>
+        <v>415682</v>
       </c>
       <c r="R4" t="n">
-        <v>6432343.782845894</v>
+        <v>6432350</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,27 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-08-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-08-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,75 +998,87 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Carin Franson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
-        </is>
-      </c>
+          <t>Carin Franson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81217235</v>
+        <v>86449933</v>
       </c>
       <c r="B5" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>219875</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Falköpings kommun, Vg</t>
+          <t>Betesmark norr om Åsarp, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>415787.0894142973</v>
+        <v>415679</v>
       </c>
       <c r="R5" t="n">
-        <v>6432398.227285175</v>
+        <v>6432348</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,27 +1102,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-08-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-08-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,37 +1116,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Carin Franson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
-        </is>
-      </c>
+          <t>Carin Franson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>86159417</v>
+        <v>86576083</v>
       </c>
       <c r="B6" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,27 +1146,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221141</v>
+        <v>219875</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1204,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>415786.027278431</v>
+        <v>415765</v>
       </c>
       <c r="R6" t="n">
-        <v>6432347.920482591</v>
+        <v>6432431</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,19 +1208,14 @@
           <t>2020-05-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-05-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>betesmark</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,58 +1242,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>86159418</v>
+        <v>81217229</v>
       </c>
       <c r="B7" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221141</v>
+        <v>220079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Betesmark norr om Åsarp, Vg</t>
+          <t>Falköpings kommun, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>415628.7820160835</v>
+        <v>415779</v>
       </c>
       <c r="R7" t="n">
-        <v>6432416.936357847</v>
+        <v>6432369</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,22 +1307,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,85 +1332,68 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Carin Franson</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carin Franson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>86449907</v>
+        <v>102267570</v>
       </c>
       <c r="B8" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219875</v>
+        <v>220079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Betesmark norr om Åsarp, Vg</t>
+          <t>Alvareds kommunala betesmark, Åsarp, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>415682.0284129048</v>
+        <v>415775</v>
       </c>
       <c r="R8" t="n">
-        <v>6432349.587793851</v>
+        <v>6432350</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,22 +1417,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,27 +1438,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Carin Franson</t>
+          <t>Dag Fredriksson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carin Franson</t>
+          <t>Dag Fredriksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>86449766</v>
+        <v>81217222</v>
       </c>
       <c r="B9" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,57 +1461,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219875</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Betesmark norr om Åsarp, Vg</t>
+          <t>Falköpings kommun, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>415681.5202521798</v>
+        <v>415778</v>
       </c>
       <c r="R9" t="n">
-        <v>6432350.658106152</v>
+        <v>6432341</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1616,22 +1515,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1640,34 +1534,32 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carin Franson</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carin Franson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>86449933</v>
+        <v>86159417</v>
       </c>
       <c r="B10" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,54 +1567,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219875</v>
+        <v>221141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Betesmark norr om Åsarp, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>415679.3420825418</v>
+        <v>415786</v>
       </c>
       <c r="R10" t="n">
-        <v>6432348.055225835</v>
+        <v>6432348</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1749,22 +1626,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,7 +1640,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1792,15 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>86576083</v>
+        <v>86159418</v>
       </c>
       <c r="B11" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,27 +1669,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219875</v>
+        <v>221141</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1837,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>415764.9582608895</v>
+        <v>415629</v>
       </c>
       <c r="R11" t="n">
-        <v>6432431.010940412</v>
+        <v>6432417</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1870,24 +1731,9 @@
           <t>2020-05-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-05-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>betesmark</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1914,15 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102267570</v>
+        <v>81217224</v>
       </c>
       <c r="B12" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,38 +1771,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Alvareds kommunala betesmark, Åsarp, Vg</t>
+          <t>Falköpings kommun, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>415775.4386536209</v>
+        <v>415656</v>
       </c>
       <c r="R12" t="n">
-        <v>6432349.203624777</v>
+        <v>6432344</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1988,22 +1825,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2012,22 +1844,25 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Dag Fredriksson</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Dag Fredriksson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
